--- a/docs/pension_data_combined_2026-09-03.xlsx
+++ b/docs/pension_data_combined_2026-09-03.xlsx
@@ -1228,7 +1228,7 @@
         <v>1.1675</v>
       </c>
       <c r="D48" t="n">
-        <v>4000394.28</v>
+        <v>4002478.6</v>
       </c>
     </row>
     <row r="49">
@@ -1246,7 +1246,7 @@
         <v>2.1887</v>
       </c>
       <c r="D49" t="n">
-        <v>71271462.55</v>
+        <v>71278596.06999999</v>
       </c>
     </row>
     <row r="50">
@@ -1264,7 +1264,7 @@
         <v>2.2078</v>
       </c>
       <c r="D50" t="n">
-        <v>232126370.95</v>
+        <v>232121782.4</v>
       </c>
     </row>
     <row r="51">
@@ -1282,7 +1282,7 @@
         <v>2.2262</v>
       </c>
       <c r="D51" t="n">
-        <v>355521463.55</v>
+        <v>355505215.5</v>
       </c>
     </row>
     <row r="52">
@@ -1300,7 +1300,7 @@
         <v>2.2308</v>
       </c>
       <c r="D52" t="n">
-        <v>433976691.89</v>
+        <v>433969480.3</v>
       </c>
     </row>
     <row r="53">
@@ -1318,7 +1318,7 @@
         <v>1.9886</v>
       </c>
       <c r="D53" t="n">
-        <v>398330839.26</v>
+        <v>398344309.6</v>
       </c>
     </row>
     <row r="54">
@@ -1336,7 +1336,7 @@
         <v>1.5442</v>
       </c>
       <c r="D54" t="n">
-        <v>321514595.36</v>
+        <v>321191929.4</v>
       </c>
     </row>
     <row r="55">
@@ -1354,7 +1354,7 @@
         <v>1.2002</v>
       </c>
       <c r="D55" t="n">
-        <v>59920784.11</v>
+        <v>59896962.42</v>
       </c>
     </row>
   </sheetData>

--- a/docs/pension_data_combined_2026-09-03.xlsx
+++ b/docs/pension_data_combined_2026-09-03.xlsx
@@ -1224,9 +1224,6 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C48" t="n">
-        <v>1.1675</v>
-      </c>
       <c r="D48" t="n">
         <v>4002478.6</v>
       </c>
@@ -1349,9 +1346,6 @@
         <is>
           <t>2026-09-03</t>
         </is>
-      </c>
-      <c r="C55" t="n">
-        <v>1.2002</v>
       </c>
       <c r="D55" t="n">
         <v>59896962.42</v>

--- a/docs/pension_data_combined_2026-09-03.xlsx
+++ b/docs/pension_data_combined_2026-09-03.xlsx
@@ -1224,6 +1224,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="C48" t="n">
+        <v>1.1675</v>
+      </c>
       <c r="D48" t="n">
         <v>4002478.6</v>
       </c>
@@ -1346,6 +1349,9 @@
         <is>
           <t>2026-09-03</t>
         </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1.2002</v>
       </c>
       <c r="D55" t="n">
         <v>59896962.42</v>
